--- a/docs/demo/quarter.xlsx
+++ b/docs/demo/quarter.xlsx
@@ -416,6 +416,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
@@ -598,6 +602,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/demo/quarter.xlsx
+++ b/docs/demo/quarter.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t xml:space="preserve">Pine Street Holdings</t>
   </si>
@@ -87,6 +87,9 @@
     <t xml:space="preserve">Amount</t>
   </si>
   <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">PS-1041</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
     <t xml:space="preserve">12 Apr</t>
   </si>
   <si>
+    <t xml:space="preserve">Paid</t>
+  </si>
+  <si>
     <t xml:space="preserve">PS-1042</t>
   </si>
   <si>
@@ -105,6 +111,9 @@
     <t xml:space="preserve">18 Apr</t>
   </si>
   <si>
+    <t xml:space="preserve">Sent</t>
+  </si>
+  <si>
     <t xml:space="preserve">PS-1043</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
   </si>
   <si>
     <t xml:space="preserve">02 May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overdue</t>
   </si>
   <si>
     <t xml:space="preserve">PS-1044</t>
@@ -253,7 +265,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -279,6 +291,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -620,7 +636,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.95"/>
@@ -640,103 +656,127 @@
       <c r="D1" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8400</v>
       </c>
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>3150</v>
       </c>
+      <c r="E3" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>12600</v>
       </c>
+      <c r="E4" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>5900</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4750</v>
       </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>6300</v>
       </c>
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="C8" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>9050</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -749,6 +789,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="One of Sent, Paid or Overdue." promptTitle="Status" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="E2:E8" type="list">
+      <formula1>"Sent,Paid,Overdue"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -773,17 +819,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
